--- a/assets/Ticket_Analysis_Master.xlsx
+++ b/assets/Ticket_Analysis_Master.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryant\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryant\Desktop\Github Projects\aura---the-l0-agent--v2\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56CB7083-9E61-48DC-A113-98DA7A4A3473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386845E2-D657-40BF-853A-51E5C89F1182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E7074128-4755-4C53-BA11-53F351F7927B}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>f</t>
+    <t xml:space="preserve">This is not the file. Not posted due to security reasons. Submitted in Ideathon portal. </t>
   </si>
 </sst>
 </file>
